--- a/excels/5. YLENS_YAHOO_FINANCE_ANALYZER_Z.xlsx
+++ b/excels/5. YLENS_YAHOO_FINANCE_ANALYZER_Z.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AMARDATA\TIGZIG\XLWINGS\excel\YFIN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AMARDATA\GITHUB\SHARED_XLWINGS_DEMO\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A0B1B2-0923-45E1-8D56-7919B57F3221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68DB80D-2D22-4AFC-ADC5-4C4BF56D4C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{528BE8C9-8211-474B-848F-0939E387E075}"/>
   </bookViews>
@@ -1391,9 +1391,6 @@
     <t>YLENS: YAHOO FINANCE ANALYZER -  PRICES</t>
   </si>
   <si>
-    <t xml:space="preserve">YLENS: YAHOO FINANCE ANALYZER -  TECHNICAL ANALYAIS </t>
-  </si>
-  <si>
     <t>YLENS: YAHOO FINANCE ANALYZER -  P&amp;L</t>
   </si>
   <si>
@@ -1404,6 +1401,9 @@
   </si>
   <si>
     <t>YLENS: YAHOO FINANCE ANALYZER -   QUARTERLIES</t>
+  </si>
+  <si>
+    <t>YLENS: YAHOO FINANCE ANALYZER -  TECHNICAL ANALYSIS</t>
   </si>
 </sst>
 </file>
@@ -2137,7 +2137,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="563" row="10">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="10">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -3814,6 +3814,7 @@
       <c r="C1" s="22"/>
       <c r="D1" s="22"/>
       <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B2"/>
@@ -8980,7 +8981,7 @@
   <sheetData>
     <row r="1" spans="1:21" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="19" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="22"/>
@@ -12305,7 +12306,7 @@
   <sheetData>
     <row r="1" spans="1:205" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="19" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="21"/>
@@ -16436,7 +16437,7 @@
   <sheetData>
     <row r="1" spans="1:205" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="19" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="21"/>
@@ -21031,7 +21032,7 @@
   <sheetData>
     <row r="1" spans="1:205" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="19" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="21"/>
@@ -25240,7 +25241,7 @@
   <sheetData>
     <row r="1" spans="1:205" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="19" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="21"/>
